--- a/artfynd/A 12711-2022 artfynd.xlsx
+++ b/artfynd/A 12711-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12711-2022 artfynd.xlsx
+++ b/artfynd/A 12711-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94342589</v>
+        <v>94365930</v>
       </c>
       <c r="B2" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>100004</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Kungsfiskare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Alcedo atthis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvillemåla, skog SV kvarnen, Sm</t>
+          <t>Kvillemåla kvarn 50m VSV, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535745.367770324</v>
+        <v>535740</v>
       </c>
       <c r="R2" t="n">
-        <v>6354045.220972053</v>
+        <v>6354051</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,19 +751,9 @@
           <t>2021-06-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,12 +768,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Roger Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström, Tommy Nilsson, Nicklas Strömberg, Lisa Petersson, Roger Karlsson, Jimmie Rundberg</t>
+          <t>Roger Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -793,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94342650</v>
+        <v>94342589</v>
       </c>
       <c r="B3" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,16 +795,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -831,14 +817,14 @@
       <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stora Kvillemålavägen, Virserum, Hultsfred, Sm</t>
+          <t>Kvillemåla, skog SV kvarnen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535720.8257608969</v>
+        <v>535745</v>
       </c>
       <c r="R3" t="n">
-        <v>6354006.136350522</v>
+        <v>6354045</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,19 +854,9 @@
           <t>2021-06-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström, Tommy Nilsson, Nicklas Strömberg, Lisa Petersson, Roger Karlsson, Jimmie Rundberg</t>
+          <t>Ingela Carlström, Jimmie Rundberg, Roger Karlsson, Lisa Petersson, Nicklas Strömberg, Tommy Nilsson, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -911,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94364469</v>
+        <v>94364432</v>
       </c>
       <c r="B4" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,16 +898,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -948,7 +919,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -959,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535739.9071193573</v>
+        <v>535740</v>
       </c>
       <c r="R4" t="n">
-        <v>6354051.111884326</v>
+        <v>6354051</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -992,24 +963,14 @@
           <t>2021-06-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-06-19</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Löv/barr område SV, 7 plantor</t>
+          <t>Löv/barr område SV</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,15 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94364432</v>
+        <v>94342650</v>
       </c>
       <c r="B5" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,16 +1013,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221141</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1075,27 +1031,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvillemåla kvarn 50m VSV, Sm</t>
+          <t>Stora Kvillemålavägen, Virserum, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535739.9071193573</v>
+        <v>535721</v>
       </c>
       <c r="R5" t="n">
-        <v>6354051.111884326</v>
+        <v>6354006</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,45 +1072,29 @@
           <t>2021-06-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-06-19</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Löv/barr område SV</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Roger Karlsson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Roger Karlsson</t>
+          <t>Ingela Carlström, Jimmie Rundberg, Roger Karlsson, Lisa Petersson, Nicklas Strömberg, Tommy Nilsson, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1171,47 +1105,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94365930</v>
+        <v>94364469</v>
       </c>
       <c r="B6" t="n">
-        <v>56387</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100004</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfiskare</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alcedo atthis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1219,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535739.9071193573</v>
+        <v>535740</v>
       </c>
       <c r="R6" t="n">
-        <v>6354051.111884326</v>
+        <v>6354051</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1252,19 +1181,14 @@
           <t>2021-06-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-06-19</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Löv/barr område SV, 7 plantor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,6 +1197,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1292,6 +1217,106 @@
           <t>Kvillemåla kvarn bioblitz</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>60267321</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kvillemåla, forsen, Virserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>535774</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6354069</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2016-06-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2016-06-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Calle Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Calle Ljungberg, Tommy Nilsson, Jimmie Rundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12711-2022 artfynd.xlsx
+++ b/artfynd/A 12711-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -781,6 +786,11 @@
           <t>Kvillemåla kvarn bioblitz</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94365930</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Kvillemåla kvarn bioblitz</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94342589</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
           <t>Kvillemåla kvarn bioblitz</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94364432</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
           <t>Kvillemåla kvarn bioblitz</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94342650</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Kvillemåla kvarn bioblitz</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94364469</t>
         </is>
       </c>
     </row>
@@ -1317,8 +1347,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60267321</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>